--- a/TIMES-NZ/v303/SuppXLS/Scen_LNG_build_timing.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Scen_LNG_build_timing.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -431,7 +431,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Integer settings for building discrete LNG ports. This is included in a scenario file which is apparently needed for discrete builds?</t>
+          <t>Build timing for LNG port, including single port unit build at 2027.</t>
         </is>
       </c>
     </row>
@@ -460,40 +460,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AllRegions</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Other_Indexes</t>
+          <t>NI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NCAP_DISC</t>
+          <t>NCAP_PASTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LNGPORTSML</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
+          <t>LNGPORTSTD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NCAP_DISC</t>
+          <t>CAP_BND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -501,56 +497,37 @@
           <t>LNGPORTSTD</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>2028</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCAP_DISC</t>
+          <t>CAP_BND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LNGPORTSML</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NCAP_DISC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>LNGPORTSTD</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
   </sheetData>
